--- a/夏作品コスト表.xlsx
+++ b/夏作品コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeraoAyato\Documents\GitHub\NatuSakuhin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9ECD6321-7CD4-4CC3-9783-36EEB730A8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318F9051-2557-47FF-A1A7-7551BF60B613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -408,17 +408,6 @@
   </si>
   <si>
     <t>　―　パンチ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　―　キック</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　－　気絶</t>
-    <rPh sb="3" eb="5">
-      <t>キゼツ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -815,8 +804,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}" name="テーブル1" displayName="テーブル1" ref="E2:E58" totalsRowShown="0" headerRowDxfId="5" dataDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="2" totalsRowBorderDxfId="1">
-  <autoFilter ref="E2:E58" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}" name="テーブル1" displayName="テーブル1" ref="E2:E56" totalsRowShown="0" headerRowDxfId="5" dataDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="2" totalsRowBorderDxfId="1">
+  <autoFilter ref="E2:E56" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{A47BB3CB-D1EF-4B37-9B3E-3ED069040864}" name="判定" dataDxfId="0"/>
   </tableColumns>
@@ -1087,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -1123,7 +1112,7 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <f>SUM(C3:C58)</f>
+        <f>SUM(C3:C56)</f>
         <v>0</v>
       </c>
     </row>
@@ -1138,7 +1127,7 @@
         <v>6</v>
       </c>
       <c r="H3">
-        <f>SUMIF(E3:E58,"完了",C3:C58)</f>
+        <f>SUMIF(E3:E56,"完了",C3:C56)</f>
         <v>0</v>
       </c>
       <c r="K3" t="s">
@@ -1160,7 +1149,7 @@
       </c>
       <c r="H4" s="2">
         <f ca="1">NETWORKDAYS(H5,H6)</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="I4" t="s">
         <v>11</v>
@@ -1171,7 +1160,7 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">_xlfn.DAYS(H6,H5)</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L4" s="3">
         <f ca="1">H3/K4</f>
@@ -1205,7 +1194,7 @@
       </c>
       <c r="H6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1284,7 +1273,7 @@
       </c>
       <c r="I13" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),H13)</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J13" s="3">
         <f ca="1">($H$2 - $H$3) / I13</f>
@@ -1292,7 +1281,7 @@
       </c>
       <c r="K13">
         <f ca="1">_xlfn.DAYS(H13,$H$6)</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L13" s="3">
         <f ca="1">($H$2 - $H$3) / K13</f>
@@ -1315,7 +1304,7 @@
       </c>
       <c r="I14" s="2">
         <f t="shared" ref="I14:I15" ca="1" si="0">NETWORKDAYS(TODAY(),H14)</f>
-        <v>-234</v>
+        <v>-235</v>
       </c>
       <c r="J14" s="3">
         <f ca="1">($H$2 - $H$3) / I14</f>
@@ -1323,7 +1312,7 @@
       </c>
       <c r="K14">
         <f t="shared" ref="K14:K15" ca="1" si="1">_xlfn.DAYS(H14,$H$6)</f>
-        <v>-327</v>
+        <v>-328</v>
       </c>
       <c r="L14" s="3">
         <f ca="1">($H$2 - $H$3) / K14</f>
@@ -1341,12 +1330,12 @@
         <v>26</v>
       </c>
       <c r="H15" s="1">
-        <f>DATE(2026,0,0)</f>
+        <f>DATE(2026,,)</f>
         <v>45991</v>
       </c>
       <c r="I15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-169</v>
+        <v>-170</v>
       </c>
       <c r="J15" s="3">
         <f ca="1">($H$2 - $H$3) / I15</f>
@@ -1354,7 +1343,7 @@
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="1"/>
-        <v>-235</v>
+        <v>-236</v>
       </c>
       <c r="L15" s="3">
         <f ca="1">($H$2 - $H$3) / K15</f>
@@ -1363,64 +1352,59 @@
     </row>
     <row r="16" spans="1:12">
       <c r="B16" s="7" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="19"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="3"/>
-      <c r="L16" s="3"/>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="19"/>
     </row>
     <row r="18" spans="2:5">
-      <c r="B18" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="19"/>
+      <c r="B18" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="21"/>
     </row>
     <row r="19" spans="2:5">
-      <c r="B19" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="19"/>
+      <c r="B19" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="26"/>
     </row>
     <row r="20" spans="2:5">
-      <c r="B20" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="21"/>
+      <c r="B20" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="29"/>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" s="8" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="26"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="30"/>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="29"/>
+      <c r="B22" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="8"/>
     </row>
     <row r="23" spans="2:5">
       <c r="B23" s="8" t="s">
@@ -1428,7 +1412,7 @@
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="28"/>
-      <c r="E23" s="30"/>
+      <c r="E23" s="31"/>
     </row>
     <row r="24" spans="2:5">
       <c r="B24" s="8" t="s">
@@ -1444,7 +1428,7 @@
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="28"/>
-      <c r="E25" s="31"/>
+      <c r="E25" s="30"/>
     </row>
     <row r="26" spans="2:5">
       <c r="B26" s="8" t="s">
@@ -1452,65 +1436,65 @@
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="28"/>
-      <c r="E26" s="8"/>
+      <c r="E26" s="19"/>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="8" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="C27" s="8"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="30"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="26"/>
     </row>
     <row r="28" spans="2:5">
-      <c r="B28" s="8" t="s">
-        <v>73</v>
-      </c>
+      <c r="B28" s="8"/>
       <c r="C28" s="8"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="19"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="26"/>
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="26"/>
     </row>
     <row r="30" spans="2:5">
-      <c r="B30" s="8"/>
+      <c r="B30" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="26"/>
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="26"/>
     </row>
     <row r="32" spans="2:5">
-      <c r="B32" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="26"/>
+      <c r="B32" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="19"/>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="26"/>
+      <c r="B33" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="19"/>
     </row>
     <row r="34" spans="2:7">
       <c r="B34" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -1518,71 +1502,71 @@
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="19"/>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="19"/>
+      <c r="B36" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="26"/>
     </row>
     <row r="37" spans="2:7">
       <c r="B37" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="19"/>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="26"/>
+      <c r="B38" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="19"/>
     </row>
     <row r="39" spans="2:7">
       <c r="B39" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="19"/>
     </row>
     <row r="40" spans="2:7">
-      <c r="B40" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="19"/>
+      <c r="B40" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="26"/>
     </row>
     <row r="41" spans="2:7">
       <c r="B41" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="19"/>
     </row>
     <row r="42" spans="2:7">
-      <c r="B42" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="26"/>
+      <c r="B42" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="19"/>
     </row>
     <row r="43" spans="2:7">
       <c r="B43" s="7" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -1590,127 +1574,111 @@
     </row>
     <row r="44" spans="2:7">
       <c r="B44" s="7" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="19"/>
     </row>
     <row r="45" spans="2:7">
-      <c r="B45" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="19"/>
+      <c r="B45" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="26"/>
+      <c r="G45" s="1"/>
     </row>
     <row r="46" spans="2:7">
       <c r="B46" s="7" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="19"/>
+      <c r="G46" s="1"/>
     </row>
     <row r="47" spans="2:7">
-      <c r="B47" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="26"/>
+      <c r="B47" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="19"/>
       <c r="G47" s="1"/>
     </row>
     <row r="48" spans="2:7">
       <c r="B48" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
       <c r="E48" s="19"/>
-      <c r="G48" s="1"/>
-    </row>
-    <row r="49" spans="2:7">
-      <c r="B49" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="19"/>
-      <c r="G49" s="1"/>
-    </row>
-    <row r="50" spans="2:7">
-      <c r="B50" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="19"/>
-    </row>
-    <row r="51" spans="2:7">
-      <c r="B51" s="10" t="s">
+    </row>
+    <row r="49" spans="2:5">
+      <c r="B49" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="22"/>
-    </row>
-    <row r="52" spans="2:7">
-      <c r="B52" s="9" t="s">
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="22"/>
+    </row>
+    <row r="50" spans="2:5">
+      <c r="B50" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="21"/>
-    </row>
-    <row r="53" spans="2:7">
-      <c r="B53" s="8" t="s">
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="21"/>
+    </row>
+    <row r="51" spans="2:5">
+      <c r="B51" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="26"/>
-    </row>
-    <row r="54" spans="2:7">
-      <c r="B54" s="7" t="s">
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="26"/>
+    </row>
+    <row r="52" spans="2:5">
+      <c r="B52" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="19"/>
-    </row>
-    <row r="55" spans="2:7">
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="19"/>
+    </row>
+    <row r="53" spans="2:5">
+      <c r="B53" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="19"/>
+    </row>
+    <row r="54" spans="2:5">
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="21"/>
+    </row>
+    <row r="55" spans="2:5">
       <c r="B55" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
-      <c r="E55" s="19"/>
-    </row>
-    <row r="56" spans="2:7">
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="21"/>
-    </row>
-    <row r="57" spans="2:7">
-      <c r="B57" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="24"/>
-    </row>
-    <row r="58" spans="2:7">
-      <c r="B58" s="7" t="s">
+      <c r="E55" s="24"/>
+    </row>
+    <row r="56" spans="2:5">
+      <c r="B56" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="7"/>
-    </row>
-    <row r="59" spans="2:7">
-      <c r="D59" s="18"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="7"/>
+    </row>
+    <row r="57" spans="2:5">
+      <c r="D57" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1743,26 +1711,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -1997,26 +1945,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EA044FE-1970-4C5E-9C63-D8FEC9524EE6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2033,4 +1982,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/夏作品コスト表.xlsx
+++ b/夏作品コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeraoAyato\Documents\GitHub\NatuSakuhin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\OneDrive\Documents\GitHub\NatuSakuhin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318F9051-2557-47FF-A1A7-7551BF60B613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88763582-F7FA-40C5-91A3-67FA9E97507D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="74">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -259,14 +259,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　―　ジャンプ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　―　ガード</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>　－　死亡</t>
     <rPh sb="3" eb="5">
       <t>シボウ</t>
@@ -403,14 +395,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>プレイヤー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　―　パンチ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>　ー　ゲームクリア画面</t>
     <rPh sb="9" eb="11">
       <t>ガメン</t>
@@ -457,6 +441,39 @@
     <t>　ー　死亡</t>
     <rPh sb="3" eb="5">
       <t>シボウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　―　パンチ1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　―　パンチ2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　―　パンチ3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・プレイヤー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　―　攻撃</t>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　―　当たり判定</t>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -507,7 +524,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -577,12 +594,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -669,7 +680,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -678,7 +689,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -690,18 +700,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -804,8 +809,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}" name="テーブル1" displayName="テーブル1" ref="E2:E56" totalsRowShown="0" headerRowDxfId="5" dataDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="2" totalsRowBorderDxfId="1">
-  <autoFilter ref="E2:E56" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}" name="テーブル1" displayName="テーブル1" ref="E2:E60" totalsRowShown="0" headerRowDxfId="5" dataDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="2" totalsRowBorderDxfId="1">
+  <autoFilter ref="E2:E60" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{A47BB3CB-D1EF-4B37-9B3E-3ED069040864}" name="判定" dataDxfId="0"/>
   </tableColumns>
@@ -1076,7 +1081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -1097,7 +1102,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="B2" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>1</v>
@@ -1105,29 +1110,31 @@
       <c r="D2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="10" t="s">
         <v>4</v>
       </c>
       <c r="H2">
-        <f>SUM(C3:C56)</f>
-        <v>0</v>
+        <f>SUM(C3:C60)</f>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
+      <c r="C3" s="8">
+        <v>1</v>
+      </c>
+      <c r="D3" s="8"/>
       <c r="E3" s="19"/>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H3">
-        <f>SUMIF(E3:E56,"完了",C3:C56)</f>
+        <f>SUMIF(E3:E60,"完了",C3:C60)</f>
         <v>0</v>
       </c>
       <c r="K3" t="s">
@@ -1141,40 +1148,44 @@
       <c r="B4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="8"/>
+      <c r="C4" s="8">
+        <v>1</v>
+      </c>
       <c r="D4" s="8"/>
-      <c r="E4" s="20"/>
-      <c r="G4" s="13" t="s">
+      <c r="E4" s="19"/>
+      <c r="G4" s="12" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="2">
         <f ca="1">NETWORKDAYS(H5,H6)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="3" t="e">
         <f ca="1" xml:space="preserve"> H3 / H4</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="K4" s="2">
         <f ca="1">_xlfn.DAYS(H6,H5)</f>
-        <v>-1</v>
-      </c>
-      <c r="L4" s="3">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="e">
         <f ca="1">H3/K4</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="8"/>
+        <v>59</v>
+      </c>
+      <c r="C5" s="8">
+        <v>3</v>
+      </c>
       <c r="D5" s="8"/>
-      <c r="E5" s="26"/>
-      <c r="G5" s="14" t="s">
+      <c r="E5" s="19"/>
+      <c r="G5" s="13" t="s">
         <v>12</v>
       </c>
       <c r="H5" s="1">
@@ -1183,67 +1194,81 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="20"/>
-      <c r="G6" s="15" t="s">
+      <c r="C6" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="18"/>
+      <c r="G6" s="14" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="21"/>
+      <c r="C7" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="18"/>
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="7"/>
+      <c r="C8" s="7">
+        <v>0.5</v>
+      </c>
       <c r="D8" s="7"/>
-      <c r="E8" s="19"/>
+      <c r="E8" s="18"/>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="7"/>
+      <c r="C9" s="7">
+        <v>0.5</v>
+      </c>
       <c r="D9" s="7"/>
-      <c r="E9" s="19"/>
+      <c r="E9" s="18"/>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="7"/>
+      <c r="C10" s="7">
+        <v>0.5</v>
+      </c>
       <c r="D10" s="7"/>
-      <c r="E10" s="19"/>
+      <c r="E10" s="18"/>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="7"/>
+      <c r="C11" s="7">
+        <v>0.5</v>
+      </c>
       <c r="D11" s="7"/>
-      <c r="E11" s="19"/>
+      <c r="E11" s="18"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="B12" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+      <c r="B12" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="8">
+        <v>21</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
       <c r="I12" t="s">
         <v>20</v>
       </c>
@@ -1261,10 +1286,14 @@
       <c r="B13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="19"/>
-      <c r="G13" s="11" t="s">
+      <c r="C13" s="7">
+        <v>3</v>
+      </c>
+      <c r="D13" s="7">
+        <v>3</v>
+      </c>
+      <c r="E13" s="18"/>
+      <c r="G13" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="1">
@@ -1273,29 +1302,31 @@
       </c>
       <c r="I13" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),H13)</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J13" s="3">
         <f ca="1">($H$2 - $H$3) / I13</f>
-        <v>0</v>
+        <v>2.4761904761904763</v>
       </c>
       <c r="K13">
         <f ca="1">_xlfn.DAYS(H13,$H$6)</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L13" s="3">
         <f ca="1">($H$2 - $H$3) / K13</f>
-        <v>0</v>
+        <v>1.7333333333333334</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="B14" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="7"/>
+        <v>72</v>
+      </c>
+      <c r="C14" s="7">
+        <v>6</v>
+      </c>
       <c r="D14" s="7"/>
-      <c r="E14" s="19"/>
-      <c r="G14" s="16" t="s">
+      <c r="E14" s="18"/>
+      <c r="G14" s="15" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="1">
@@ -1308,25 +1339,27 @@
       </c>
       <c r="J14" s="3">
         <f ca="1">($H$2 - $H$3) / I14</f>
-        <v>0</v>
+        <v>-0.22127659574468084</v>
       </c>
       <c r="K14">
         <f t="shared" ref="K14:K15" ca="1" si="1">_xlfn.DAYS(H14,$H$6)</f>
-        <v>-328</v>
+        <v>-329</v>
       </c>
       <c r="L14" s="3">
         <f ca="1">($H$2 - $H$3) / K14</f>
-        <v>0</v>
+        <v>-0.1580547112462006</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="B15" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="7"/>
+        <v>68</v>
+      </c>
+      <c r="C15" s="7">
+        <v>3</v>
+      </c>
       <c r="D15" s="7"/>
-      <c r="E15" s="19"/>
-      <c r="G15" s="17" t="s">
+      <c r="E15" s="18"/>
+      <c r="G15" s="16" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="1">
@@ -1339,346 +1372,386 @@
       </c>
       <c r="J15" s="3">
         <f ca="1">($H$2 - $H$3) / I15</f>
-        <v>0</v>
+        <v>-0.30588235294117649</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="1"/>
-        <v>-236</v>
+        <v>-237</v>
       </c>
       <c r="L15" s="3">
         <f ca="1">($H$2 - $H$3) / K15</f>
-        <v>0</v>
+        <v>-0.21940928270042195</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="B16" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="7"/>
+        <v>73</v>
+      </c>
+      <c r="C16" s="7">
+        <v>3</v>
+      </c>
       <c r="D16" s="7"/>
-      <c r="E16" s="19"/>
+      <c r="E16" s="18"/>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="7"/>
+        <v>69</v>
+      </c>
+      <c r="C17" s="7">
+        <v>3</v>
+      </c>
       <c r="D17" s="7"/>
-      <c r="E17" s="19"/>
+      <c r="E17" s="18"/>
     </row>
     <row r="18" spans="2:5">
-      <c r="B18" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="21"/>
+      <c r="B18" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="18"/>
     </row>
     <row r="19" spans="2:5">
-      <c r="B19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="26"/>
+      <c r="B19" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="18"/>
     </row>
     <row r="20" spans="2:5">
-      <c r="B20" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="29"/>
+      <c r="B20" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="18"/>
     </row>
     <row r="21" spans="2:5">
-      <c r="B21" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="30"/>
+      <c r="B21" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="7">
+        <v>2</v>
+      </c>
+      <c r="D21" s="7"/>
+      <c r="E21" s="18"/>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="8"/>
+      <c r="B22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="7">
+        <v>3</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="E22" s="18"/>
     </row>
     <row r="23" spans="2:5">
       <c r="B23" s="8" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C23" s="8"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="31"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="19"/>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="8"/>
+      <c r="B24" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="22"/>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="30"/>
+      <c r="B25" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="7"/>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="19"/>
+      <c r="B26" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="7"/>
     </row>
     <row r="27" spans="2:5">
-      <c r="B27" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="26"/>
+      <c r="B27" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="24"/>
     </row>
     <row r="28" spans="2:5">
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="26"/>
+      <c r="B28" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="7"/>
     </row>
     <row r="29" spans="2:5">
-      <c r="B29" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="26"/>
+      <c r="B29" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="7"/>
     </row>
     <row r="30" spans="2:5">
-      <c r="B30" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="26"/>
+      <c r="B30" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="18"/>
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
-      <c r="E31" s="26"/>
+      <c r="E31" s="19"/>
     </row>
     <row r="32" spans="2:5">
-      <c r="B32" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
-      <c r="E32" s="19"/>
-    </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
+      <c r="E32" s="18"/>
+    </row>
+    <row r="33" spans="2:5">
+      <c r="B33" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
       <c r="E33" s="19"/>
     </row>
-    <row r="34" spans="2:7">
+    <row r="34" spans="2:5">
       <c r="B34" s="7" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
-      <c r="E34" s="19"/>
-    </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
+      <c r="E34" s="18"/>
+    </row>
+    <row r="35" spans="2:5">
+      <c r="B35" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
       <c r="E35" s="19"/>
     </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="26"/>
-    </row>
-    <row r="37" spans="2:7">
+    <row r="36" spans="2:5">
+      <c r="B36" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="18"/>
+    </row>
+    <row r="37" spans="2:5">
       <c r="B37" s="7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
-      <c r="E37" s="19"/>
-    </row>
-    <row r="38" spans="2:7">
+      <c r="E37" s="18"/>
+    </row>
+    <row r="38" spans="2:5">
       <c r="B38" s="7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
-      <c r="E38" s="19"/>
-    </row>
-    <row r="39" spans="2:7">
+      <c r="E38" s="18"/>
+    </row>
+    <row r="39" spans="2:5">
       <c r="B39" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
-      <c r="E39" s="19"/>
-    </row>
-    <row r="40" spans="2:7">
+      <c r="E39" s="18"/>
+    </row>
+    <row r="40" spans="2:5">
       <c r="B40" s="8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
-      <c r="E40" s="26"/>
-    </row>
-    <row r="41" spans="2:7">
+      <c r="E40" s="19"/>
+    </row>
+    <row r="41" spans="2:5">
       <c r="B41" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
-      <c r="E41" s="19"/>
-    </row>
-    <row r="42" spans="2:7">
+      <c r="E41" s="18"/>
+    </row>
+    <row r="42" spans="2:5">
       <c r="B42" s="7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
-      <c r="E42" s="19"/>
-    </row>
-    <row r="43" spans="2:7">
+      <c r="E42" s="18"/>
+    </row>
+    <row r="43" spans="2:5">
       <c r="B43" s="7" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
-      <c r="E43" s="19"/>
-    </row>
-    <row r="44" spans="2:7">
-      <c r="B44" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
+      <c r="E43" s="18"/>
+    </row>
+    <row r="44" spans="2:5">
+      <c r="B44" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
       <c r="E44" s="19"/>
     </row>
-    <row r="45" spans="2:7">
-      <c r="B45" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="26"/>
-      <c r="G45" s="1"/>
-    </row>
-    <row r="46" spans="2:7">
+    <row r="45" spans="2:5">
+      <c r="B45" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="18"/>
+    </row>
+    <row r="46" spans="2:5">
       <c r="B46" s="7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
-      <c r="E46" s="19"/>
-      <c r="G46" s="1"/>
-    </row>
-    <row r="47" spans="2:7">
+      <c r="E46" s="18"/>
+    </row>
+    <row r="47" spans="2:5">
       <c r="B47" s="7" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
-      <c r="E47" s="19"/>
-      <c r="G47" s="1"/>
-    </row>
-    <row r="48" spans="2:7">
+      <c r="E47" s="18"/>
+    </row>
+    <row r="48" spans="2:5">
       <c r="B48" s="7" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
-      <c r="E48" s="19"/>
-    </row>
-    <row r="49" spans="2:5">
-      <c r="B49" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="22"/>
-    </row>
-    <row r="50" spans="2:5">
-      <c r="B50" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="21"/>
-    </row>
-    <row r="51" spans="2:5">
-      <c r="B51" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="26"/>
-    </row>
-    <row r="52" spans="2:5">
+      <c r="E48" s="18"/>
+    </row>
+    <row r="49" spans="2:7">
+      <c r="B49" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="19"/>
+      <c r="G49" s="1"/>
+    </row>
+    <row r="50" spans="2:7">
+      <c r="B50" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="18"/>
+      <c r="G50" s="1"/>
+    </row>
+    <row r="51" spans="2:7">
+      <c r="B51" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="18"/>
+      <c r="G51" s="1"/>
+    </row>
+    <row r="52" spans="2:7">
       <c r="B52" s="7" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
-      <c r="E52" s="19"/>
-    </row>
-    <row r="53" spans="2:5">
-      <c r="B53" s="7" t="s">
+      <c r="E52" s="18"/>
+    </row>
+    <row r="53" spans="2:7">
+      <c r="B53" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="20"/>
+    </row>
+    <row r="54" spans="2:7">
+      <c r="B54" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="19"/>
+    </row>
+    <row r="55" spans="2:7">
+      <c r="B55" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="19"/>
+    </row>
+    <row r="56" spans="2:7">
+      <c r="B56" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="18"/>
+    </row>
+    <row r="57" spans="2:7">
+      <c r="B57" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="18"/>
+    </row>
+    <row r="58" spans="2:7">
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="19"/>
+    </row>
+    <row r="59" spans="2:7">
+      <c r="B59" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="22"/>
+    </row>
+    <row r="60" spans="2:7">
+      <c r="B60" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="19"/>
-    </row>
-    <row r="54" spans="2:5">
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="21"/>
-    </row>
-    <row r="55" spans="2:5">
-      <c r="B55" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="24"/>
-    </row>
-    <row r="56" spans="2:5">
-      <c r="B56" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C56" s="7"/>
-      <c r="D56" s="27"/>
-      <c r="E56" s="7"/>
-    </row>
-    <row r="57" spans="2:5">
-      <c r="D57" s="18"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="25"/>
+      <c r="E60" s="8"/>
+    </row>
+    <row r="61" spans="2:7">
+      <c r="D61" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1946,15 +2019,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
@@ -1963,6 +2027,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1985,14 +2058,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2001,4 +2066,12 @@
     <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/夏作品コスト表.xlsx
+++ b/夏作品コスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\OneDrive\Documents\GitHub\NatuSakuhin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeraoAyato\Documents\GitHub\NatuSakuhin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88763582-F7FA-40C5-91A3-67FA9E97507D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACC0E8F-1CA4-4B8A-8976-4DE3BEE6DEFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="66">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -280,24 +280,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　―　AI</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・アニメーション処理</t>
-    <rPh sb="8" eb="10">
-      <t>ショリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・カメラ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　ー　移動</t>
-  </si>
-  <si>
     <t>・マップ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -362,9 +344,6 @@
     <t>　ー　プレイヤー操作</t>
   </si>
   <si>
-    <t>　ー　カメラ操作</t>
-  </si>
-  <si>
     <t>・エフェクト</t>
   </si>
   <si>
@@ -409,42 +388,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　ー　歩く</t>
-    <rPh sb="3" eb="4">
-      <t>アル</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　ー　殴る</t>
-    <rPh sb="3" eb="4">
-      <t>ナグ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　ー　パンチ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　ー　キック</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　ー　気絶</t>
-    <rPh sb="3" eb="5">
-      <t>キゼツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　ー　死亡</t>
-    <rPh sb="3" eb="5">
-      <t>シボウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>　―　パンチ1</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -475,6 +418,24 @@
     <rPh sb="6" eb="8">
       <t>ハンテイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完了</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未完</t>
+    <rPh sb="0" eb="2">
+      <t>ミカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　ー　AI</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -486,7 +447,7 @@
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -515,12 +476,6 @@
       <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Yu Gothic"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -598,7 +553,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -619,19 +574,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -680,7 +622,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -690,23 +632,20 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -809,8 +748,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}" name="テーブル1" displayName="テーブル1" ref="E2:E60" totalsRowShown="0" headerRowDxfId="5" dataDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="2" totalsRowBorderDxfId="1">
-  <autoFilter ref="E2:E60" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}" name="テーブル1" displayName="テーブル1" ref="E2:E48" totalsRowShown="0" headerRowDxfId="5" dataDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="2" totalsRowBorderDxfId="1">
+  <autoFilter ref="E2:E48" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{A47BB3CB-D1EF-4B37-9B3E-3ED069040864}" name="判定" dataDxfId="0"/>
   </tableColumns>
@@ -1081,7 +1020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -1102,7 +1041,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="B2" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>1</v>
@@ -1110,15 +1049,15 @@
       <c r="D2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="9" t="s">
         <v>4</v>
       </c>
       <c r="H2">
-        <f>SUM(C3:C60)</f>
-        <v>52</v>
+        <f>SUM(C3:C48)</f>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1129,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="D3" s="8"/>
-      <c r="E3" s="19"/>
-      <c r="G3" s="11" t="s">
+      <c r="E3" s="17"/>
+      <c r="G3" s="10" t="s">
         <v>6</v>
       </c>
       <c r="H3">
-        <f>SUMIF(E3:E60,"完了",C3:C60)</f>
-        <v>0</v>
+        <f>SUMIF(E3:E48,"完了",C3:C48)</f>
+        <v>5.5</v>
       </c>
       <c r="K3" t="s">
         <v>7</v>
@@ -1151,41 +1090,48 @@
       <c r="C4" s="8">
         <v>1</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="19"/>
-      <c r="G4" s="12" t="s">
+      <c r="D4" s="8">
+        <v>1</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="2">
         <f ca="1">NETWORKDAYS(H5,H6)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="3" t="e">
+      <c r="J4" s="3">
         <f ca="1" xml:space="preserve"> H3 / H4</f>
-        <v>#DIV/0!</v>
+        <v>2.75</v>
       </c>
       <c r="K4" s="2">
         <f ca="1">_xlfn.DAYS(H6,H5)</f>
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="e">
+        <v>3</v>
+      </c>
+      <c r="L4" s="3">
         <f ca="1">H3/K4</f>
-        <v>#DIV/0!</v>
+        <v>1.8333333333333333</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C5" s="8">
-        <v>3</v>
+        <f>SUM(C6:C11)</f>
+        <v>3.5</v>
       </c>
       <c r="D5" s="8"/>
-      <c r="E5" s="19"/>
-      <c r="G5" s="13" t="s">
+      <c r="E5" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="12" t="s">
         <v>12</v>
       </c>
       <c r="H5" s="1">
@@ -1198,16 +1144,20 @@
         <v>13</v>
       </c>
       <c r="C6" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="18"/>
-      <c r="G6" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7">
+        <v>1</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46228</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1217,8 +1167,12 @@
       <c r="C7" s="7">
         <v>0.5</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="18"/>
+      <c r="D7" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="7" t="s">
@@ -1228,7 +1182,9 @@
         <v>0.5</v>
       </c>
       <c r="D8" s="7"/>
-      <c r="E8" s="18"/>
+      <c r="E8" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" s="7" t="s">
@@ -1238,7 +1194,9 @@
         <v>0.5</v>
       </c>
       <c r="D9" s="7"/>
-      <c r="E9" s="18"/>
+      <c r="E9" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="7" t="s">
@@ -1248,7 +1206,9 @@
         <v>0.5</v>
       </c>
       <c r="D10" s="7"/>
-      <c r="E10" s="18"/>
+      <c r="E10" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" s="7" t="s">
@@ -1258,17 +1218,22 @@
         <v>0.5</v>
       </c>
       <c r="D11" s="7"/>
-      <c r="E11" s="18"/>
+      <c r="E11" s="16" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="12" spans="1:12">
       <c r="B12" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C12" s="8">
-        <v>21</v>
+        <f>SUM(C13:C22)</f>
+        <v>26</v>
       </c>
       <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
+      <c r="E12" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="I12" t="s">
         <v>20</v>
       </c>
@@ -1292,8 +1257,10 @@
       <c r="D13" s="7">
         <v>3</v>
       </c>
-      <c r="E13" s="18"/>
-      <c r="G13" s="10" t="s">
+      <c r="E13" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="9" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="1">
@@ -1302,31 +1269,33 @@
       </c>
       <c r="I13" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),H13)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J13" s="3">
         <f ca="1">($H$2 - $H$3) / I13</f>
-        <v>2.4761904761904763</v>
+        <v>2.7749999999999999</v>
       </c>
       <c r="K13">
         <f ca="1">_xlfn.DAYS(H13,$H$6)</f>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L13" s="3">
         <f ca="1">($H$2 - $H$3) / K13</f>
-        <v>1.7333333333333334</v>
+        <v>2.0555555555555554</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="B14" s="7" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C14" s="7">
         <v>6</v>
       </c>
       <c r="D14" s="7"/>
-      <c r="E14" s="18"/>
-      <c r="G14" s="15" t="s">
+      <c r="E14" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="14" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="1">
@@ -1335,31 +1304,33 @@
       </c>
       <c r="I14" s="2">
         <f t="shared" ref="I14:I15" ca="1" si="0">NETWORKDAYS(TODAY(),H14)</f>
-        <v>-235</v>
+        <v>-237</v>
       </c>
       <c r="J14" s="3">
         <f ca="1">($H$2 - $H$3) / I14</f>
-        <v>-0.22127659574468084</v>
+        <v>-0.23417721518987342</v>
       </c>
       <c r="K14">
         <f t="shared" ref="K14:K15" ca="1" si="1">_xlfn.DAYS(H14,$H$6)</f>
-        <v>-329</v>
+        <v>-332</v>
       </c>
       <c r="L14" s="3">
         <f ca="1">($H$2 - $H$3) / K14</f>
-        <v>-0.1580547112462006</v>
+        <v>-0.16716867469879518</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="B15" s="7" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C15" s="7">
         <v>3</v>
       </c>
       <c r="D15" s="7"/>
-      <c r="E15" s="18"/>
-      <c r="G15" s="16" t="s">
+      <c r="E15" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="11" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="1">
@@ -1368,64 +1339,76 @@
       </c>
       <c r="I15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-170</v>
+        <v>-172</v>
       </c>
       <c r="J15" s="3">
         <f ca="1">($H$2 - $H$3) / I15</f>
-        <v>-0.30588235294117649</v>
+        <v>-0.32267441860465118</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="1"/>
-        <v>-237</v>
+        <v>-240</v>
       </c>
       <c r="L15" s="3">
         <f ca="1">($H$2 - $H$3) / K15</f>
-        <v>-0.21940928270042195</v>
+        <v>-0.23125000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="B16" s="7" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C16" s="7">
         <v>3</v>
       </c>
       <c r="D16" s="7"/>
-      <c r="E16" s="18"/>
+      <c r="E16" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="7" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C17" s="7">
         <v>3</v>
       </c>
       <c r="D17" s="7"/>
-      <c r="E17" s="18"/>
+      <c r="E17" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="7" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
-      <c r="E18" s="18"/>
+      <c r="E18" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="7"/>
+        <v>59</v>
+      </c>
+      <c r="C19" s="7">
+        <v>3</v>
+      </c>
       <c r="D19" s="7"/>
-      <c r="E19" s="18"/>
+      <c r="E19" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="7" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="18"/>
+      <c r="E20" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" s="7" t="s">
@@ -1435,7 +1418,9 @@
         <v>2</v>
       </c>
       <c r="D21" s="7"/>
-      <c r="E21" s="18"/>
+      <c r="E21" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="7" t="s">
@@ -1445,7 +1430,9 @@
         <v>3</v>
       </c>
       <c r="D22" s="7"/>
-      <c r="E22" s="18"/>
+      <c r="E22" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="23" spans="2:5">
       <c r="B23" s="8" t="s">
@@ -1453,305 +1440,265 @@
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
-      <c r="E23" s="19"/>
+      <c r="E23" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="24" spans="2:5">
       <c r="B24" s="7" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
-      <c r="E24" s="22"/>
+      <c r="E24" s="19" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="7"/>
+      <c r="B25" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="26" spans="2:5">
       <c r="B26" s="7" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="C26" s="7"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="7" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="C27" s="7"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="24"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="7" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="C28" s="7"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="7" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="C29" s="7"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="30" spans="2:5">
-      <c r="B30" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="18"/>
+      <c r="B30" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="31" spans="2:5">
-      <c r="B31" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="19"/>
+      <c r="B31" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="32" spans="2:5">
-      <c r="B32" s="7"/>
+      <c r="B32" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
-      <c r="E32" s="18"/>
-    </row>
-    <row r="33" spans="2:5">
-      <c r="B33" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="19"/>
-    </row>
-    <row r="34" spans="2:5">
-      <c r="B34" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="18"/>
-    </row>
-    <row r="35" spans="2:5">
-      <c r="B35" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="19"/>
-    </row>
-    <row r="36" spans="2:5">
+      <c r="E32" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
       <c r="B36" s="7" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
-      <c r="E36" s="18"/>
-    </row>
-    <row r="37" spans="2:5">
+      <c r="E36" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
       <c r="B37" s="7" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
-      <c r="E37" s="18"/>
-    </row>
-    <row r="38" spans="2:5">
+      <c r="E37" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
       <c r="B38" s="7" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
-      <c r="E38" s="18"/>
-    </row>
-    <row r="39" spans="2:5">
-      <c r="B39" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="18"/>
-    </row>
-    <row r="40" spans="2:5">
-      <c r="B40" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="19"/>
-    </row>
-    <row r="41" spans="2:5">
+      <c r="E38" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="B40" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G40" s="1"/>
+    </row>
+    <row r="41" spans="2:7">
       <c r="B41" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
-      <c r="E41" s="18"/>
-    </row>
-    <row r="42" spans="2:5">
+      <c r="E41" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G41" s="1"/>
+    </row>
+    <row r="42" spans="2:7">
       <c r="B42" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
-      <c r="E42" s="18"/>
-    </row>
-    <row r="43" spans="2:5">
-      <c r="B43" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="18"/>
-    </row>
-    <row r="44" spans="2:5">
+      <c r="E42" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7">
+      <c r="B43" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="22" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7">
       <c r="B44" s="8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
-      <c r="E44" s="19"/>
-    </row>
-    <row r="45" spans="2:5">
+      <c r="E44" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7">
       <c r="B45" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
-      <c r="E45" s="18"/>
-    </row>
-    <row r="46" spans="2:5">
+      <c r="E45" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7">
       <c r="B46" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
-      <c r="E46" s="18"/>
-    </row>
-    <row r="47" spans="2:5">
+      <c r="E46" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7">
       <c r="B47" s="7" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
-      <c r="E47" s="18"/>
-    </row>
-    <row r="48" spans="2:5">
-      <c r="B48" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="18"/>
-    </row>
-    <row r="49" spans="2:7">
-      <c r="B49" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="19"/>
-      <c r="G49" s="1"/>
-    </row>
-    <row r="50" spans="2:7">
-      <c r="B50" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="18"/>
-      <c r="G50" s="1"/>
-    </row>
-    <row r="51" spans="2:7">
-      <c r="B51" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="18"/>
-      <c r="G51" s="1"/>
-    </row>
-    <row r="52" spans="2:7">
-      <c r="B52" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="18"/>
-    </row>
-    <row r="53" spans="2:7">
-      <c r="B53" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="20"/>
-    </row>
-    <row r="54" spans="2:7">
-      <c r="B54" s="8" t="s">
+      <c r="E47" s="19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7">
+      <c r="B48" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="19"/>
-    </row>
-    <row r="55" spans="2:7">
-      <c r="B55" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="19"/>
-    </row>
-    <row r="56" spans="2:7">
-      <c r="B56" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="18"/>
-    </row>
-    <row r="57" spans="2:7">
-      <c r="B57" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="18"/>
-    </row>
-    <row r="58" spans="2:7">
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="19"/>
-    </row>
-    <row r="59" spans="2:7">
-      <c r="B59" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="22"/>
-    </row>
-    <row r="60" spans="2:7">
-      <c r="B60" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C60" s="8"/>
-      <c r="D60" s="25"/>
-      <c r="E60" s="8"/>
-    </row>
-    <row r="61" spans="2:7">
-      <c r="D61" s="17"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="4:4">
+      <c r="D49" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1784,6 +1731,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -2018,27 +1985,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EA044FE-1970-4C5E-9C63-D8FEC9524EE6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2055,23 +2021,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/夏作品コスト表.xlsx
+++ b/夏作品コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeraoAyato\Documents\GitHub\NatuSakuhin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\OneDrive\Documents\GitHub\FightingRush\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACC0E8F-1CA4-4B8A-8976-4DE3BEE6DEFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E192EA-00A6-44AE-B56C-27C85EE6E72D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="68">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -273,13 +273,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・敵</t>
-    <rPh sb="1" eb="2">
-      <t>テキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・マップ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -436,6 +429,21 @@
   </si>
   <si>
     <t>　ー　AI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ザコ敵</t>
+    <rPh sb="3" eb="4">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・　ボス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　ー AI</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -748,8 +756,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}" name="テーブル1" displayName="テーブル1" ref="E2:E48" totalsRowShown="0" headerRowDxfId="5" dataDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="2" totalsRowBorderDxfId="1">
-  <autoFilter ref="E2:E48" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}" name="テーブル1" displayName="テーブル1" ref="E2:E50" totalsRowShown="0" headerRowDxfId="5" dataDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="2" totalsRowBorderDxfId="1">
+  <autoFilter ref="E2:E50" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{A47BB3CB-D1EF-4B37-9B3E-3ED069040864}" name="判定" dataDxfId="0"/>
   </tableColumns>
@@ -1020,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -1041,7 +1049,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="B2" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>1</v>
@@ -1056,8 +1064,8 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <f>SUM(C3:C48)</f>
-        <v>61</v>
+        <f>SUM(C3:C50)</f>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1073,8 +1081,8 @@
         <v>6</v>
       </c>
       <c r="H3">
-        <f>SUMIF(E3:E48,"完了",C3:C48)</f>
-        <v>5.5</v>
+        <f>SUMIF(E3:E50,"完了",C3:C50)</f>
+        <v>14.5</v>
       </c>
       <c r="K3" t="s">
         <v>7</v>
@@ -1094,34 +1102,34 @@
         <v>1</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="2">
         <f ca="1">NETWORKDAYS(H5,H6)</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I4" t="s">
         <v>11</v>
       </c>
       <c r="J4" s="3">
         <f ca="1" xml:space="preserve"> H3 / H4</f>
-        <v>2.75</v>
+        <v>1.8125</v>
       </c>
       <c r="K4" s="2">
         <f ca="1">_xlfn.DAYS(H6,H5)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L4" s="3">
         <f ca="1">H3/K4</f>
-        <v>1.8333333333333333</v>
+        <v>1.3181818181818181</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" s="8">
         <f>SUM(C6:C11)</f>
@@ -1129,7 +1137,7 @@
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>12</v>
@@ -1150,14 +1158,14 @@
         <v>1</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G6" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46231</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1171,7 +1179,7 @@
         <v>0.5</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1183,7 +1191,7 @@
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1195,7 +1203,7 @@
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1207,7 +1215,7 @@
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1219,12 +1227,12 @@
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="B12" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" s="8">
         <f>SUM(C13:C22)</f>
@@ -1232,7 +1240,7 @@
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I12" t="s">
         <v>20</v>
@@ -1258,7 +1266,7 @@
         <v>3</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>24</v>
@@ -1269,66 +1277,66 @@
       </c>
       <c r="I13" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),H13)</f>
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J13" s="3">
         <f ca="1">($H$2 - $H$3) / I13</f>
-        <v>2.7749999999999999</v>
+        <v>3.8928571428571428</v>
       </c>
       <c r="K13">
         <f ca="1">_xlfn.DAYS(H13,$H$6)</f>
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L13" s="3">
         <f ca="1">($H$2 - $H$3) / K13</f>
-        <v>2.0555555555555554</v>
+        <v>2.8684210526315788</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="B14" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C14" s="7">
         <v>6</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G14" s="14" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="1">
-        <f>DATE(2025,8,30)</f>
-        <v>45899</v>
+        <f>DATE(2026,8,30)</f>
+        <v>46264</v>
       </c>
       <c r="I14" s="2">
         <f t="shared" ref="I14:I15" ca="1" si="0">NETWORKDAYS(TODAY(),H14)</f>
-        <v>-237</v>
+        <v>18</v>
       </c>
       <c r="J14" s="3">
         <f ca="1">($H$2 - $H$3) / I14</f>
-        <v>-0.23417721518987342</v>
+        <v>3.0277777777777777</v>
       </c>
       <c r="K14">
         <f t="shared" ref="K14:K15" ca="1" si="1">_xlfn.DAYS(H14,$H$6)</f>
-        <v>-332</v>
+        <v>25</v>
       </c>
       <c r="L14" s="3">
         <f ca="1">($H$2 - $H$3) / K14</f>
-        <v>-0.16716867469879518</v>
+        <v>2.1800000000000002</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="B15" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C15" s="7">
         <v>3</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>26</v>
@@ -1339,75 +1347,75 @@
       </c>
       <c r="I15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-172</v>
+        <v>-178</v>
       </c>
       <c r="J15" s="3">
         <f ca="1">($H$2 - $H$3) / I15</f>
-        <v>-0.32267441860465118</v>
+        <v>-0.3061797752808989</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="1"/>
-        <v>-240</v>
+        <v>-248</v>
       </c>
       <c r="L15" s="3">
         <f ca="1">($H$2 - $H$3) / K15</f>
-        <v>-0.23125000000000001</v>
+        <v>-0.21975806451612903</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="B16" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C16" s="7">
         <v>3</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C17" s="7">
         <v>3</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C19" s="7">
         <v>3</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="2:5">
@@ -1419,7 +1427,7 @@
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="2:5">
@@ -1431,274 +1439,292 @@
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="B23" s="8" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="B24" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="7"/>
+        <v>64</v>
+      </c>
+      <c r="C24" s="7">
+        <v>8</v>
+      </c>
       <c r="D24" s="7"/>
       <c r="E24" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="17" t="s">
-        <v>64</v>
-      </c>
+      <c r="B25" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="16"/>
     </row>
     <row r="26" spans="2:5">
       <c r="B26" s="7" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
-      <c r="E26" s="16" t="s">
-        <v>64</v>
-      </c>
+      <c r="E26" s="16"/>
     </row>
     <row r="27" spans="2:5">
-      <c r="B27" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="16" t="s">
-        <v>64</v>
+      <c r="B27" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="17" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="2:5">
-      <c r="B30" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="17" t="s">
-        <v>64</v>
+      <c r="B30" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="16" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="2:5">
-      <c r="B32" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="16" t="s">
-        <v>64</v>
+      <c r="B32" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="17" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="17" t="s">
-        <v>64</v>
+      <c r="B34" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="16" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="16" t="s">
-        <v>64</v>
+      <c r="B36" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="17" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="2:7">
       <c r="B37" s="7" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="2:7">
       <c r="B38" s="7" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="2:7">
-      <c r="B39" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="G39" s="1"/>
+      <c r="B39" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="16" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="40" spans="2:7">
       <c r="B40" s="7" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G40" s="1"/>
+        <v>63</v>
+      </c>
     </row>
     <row r="41" spans="2:7">
-      <c r="B41" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="16" t="s">
-        <v>64</v>
+      <c r="B41" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="17" t="s">
+        <v>63</v>
       </c>
       <c r="G41" s="1"/>
     </row>
     <row r="42" spans="2:7">
       <c r="B42" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="16" t="s">
-        <v>64</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="G42" s="1"/>
     </row>
     <row r="43" spans="2:7">
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G43" s="1"/>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7">
+      <c r="B45" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7">
+      <c r="B46" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="22" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7">
-      <c r="B44" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="45" spans="2:7">
-      <c r="B45" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7">
-      <c r="B46" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="16" t="s">
-        <v>64</v>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="17" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="2:7">
       <c r="B47" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
-      <c r="E47" s="19" t="s">
-        <v>64</v>
+      <c r="E47" s="16" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="48" spans="2:7">
-      <c r="B48" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C48" s="8"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="49" spans="4:4">
-      <c r="D49" s="15"/>
+      <c r="B48" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5">
+      <c r="B49" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5">
+      <c r="B50" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C50" s="8"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5">
+      <c r="D51" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1731,26 +1757,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -1985,10 +1991,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EA044FE-1970-4C5E-9C63-D8FEC9524EE6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2005,20 +2042,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EA044FE-1970-4C5E-9C63-D8FEC9524EE6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>